--- a/survey_templates/035_solo_performer_training_survey--survey_templates.xlsx
+++ b/survey_templates/035_solo_performer_training_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improve_technique'}</t>
+          <t>improve_technique</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improve technique'}</t>
+          <t>Improve technique</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'increase_performance'}</t>
+          <t>increase_performance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Increase performance'}</t>
+          <t>Increase performance</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'emotional'}</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Emotional'}</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
